--- a/docs/stakeholder_matrix_ahp.xlsx
+++ b/docs/stakeholder_matrix_ahp.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scalere1\OneDrive - Tallinna Tehnikaülikool\Taltech campus dataset\AHP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livettu-my.sharepoint.com/personal/edoard_taltech_ee/Documents/Documents/GitHub/AHP/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A18DC8A5-AB85-4D12-A420-8677C252622A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{A18DC8A5-AB85-4D12-A420-8677C252622A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4C8C8E3-AB6A-4ED2-9D73-5FE92D01CD00}"/>
   <bookViews>
-    <workbookView xWindow="5295" yWindow="2175" windowWidth="27240" windowHeight="17205" xr2:uid="{198BE654-42EA-4543-B053-C3E99F435526}"/>
+    <workbookView xWindow="7650" yWindow="22680" windowWidth="23730" windowHeight="15570" xr2:uid="{198BE654-42EA-4543-B053-C3E99F435526}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -346,9 +346,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="12" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="12" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -358,11 +355,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -475,6 +475,139 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="92D050"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-DA67-49A4-9310-14153BD1D22E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-DA67-49A4-9310-14153BD1D22E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-DA67-49A4-9310-14153BD1D22E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-DA67-49A4-9310-14153BD1D22E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-DA67-49A4-9310-14153BD1D22E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-DA67-49A4-9310-14153BD1D22E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000006-DA67-49A4-9310-14153BD1D22E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -1705,21 +1838,21 @@
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="K6" s="39" t="s">
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="K6" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="39"/>
+      <c r="L6" s="38"/>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
@@ -1747,149 +1880,149 @@
       <c r="I7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="40" t="s">
+      <c r="K7" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="L7" s="40"/>
-      <c r="M7" s="38"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="37"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="35" cm="1">
+      <c r="B8" s="34" cm="1">
         <f t="array" ref="B8">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>1</v>
       </c>
-      <c r="C8" s="33">
-        <v>1</v>
-      </c>
-      <c r="D8" s="33">
-        <v>1</v>
-      </c>
-      <c r="E8" s="33">
+      <c r="C8" s="32">
+        <v>1</v>
+      </c>
+      <c r="D8" s="32">
+        <v>1</v>
+      </c>
+      <c r="E8" s="32">
         <v>5</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="32">
         <v>2</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="32">
         <v>7</v>
       </c>
-      <c r="H8" s="33">
+      <c r="H8" s="32">
         <v>7</v>
       </c>
-      <c r="I8" s="34">
+      <c r="I8" s="33">
         <v>2</v>
       </c>
-      <c r="K8" s="40"/>
-      <c r="L8" s="40"/>
-      <c r="M8" s="38"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="37"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="35" cm="1">
+      <c r="B9" s="34" cm="1">
         <f t="array" ref="B9">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>1</v>
       </c>
-      <c r="C9" s="35" cm="1">
+      <c r="C9" s="34" cm="1">
         <f t="array" ref="C9">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>1</v>
       </c>
-      <c r="D9" s="33">
-        <v>1</v>
-      </c>
-      <c r="E9" s="33">
+      <c r="D9" s="32">
+        <v>1</v>
+      </c>
+      <c r="E9" s="32">
         <v>4</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="32">
         <v>2</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="32">
         <v>2</v>
       </c>
-      <c r="H9" s="33">
+      <c r="H9" s="32">
         <v>7</v>
       </c>
-      <c r="I9" s="34">
+      <c r="I9" s="33">
         <v>4</v>
       </c>
-      <c r="K9" s="40"/>
-      <c r="L9" s="40"/>
-      <c r="M9" s="38"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="37"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="35" cm="1">
+      <c r="B10" s="34" cm="1">
         <f t="array" ref="B10">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>1</v>
       </c>
-      <c r="C10" s="35" cm="1">
+      <c r="C10" s="34" cm="1">
         <f t="array" ref="C10">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>1</v>
       </c>
-      <c r="D10" s="35" cm="1">
+      <c r="D10" s="34" cm="1">
         <f t="array" ref="D10">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>1</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="32">
         <v>3</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="32">
         <v>2</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="32">
         <v>6</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10" s="32">
         <v>3</v>
       </c>
-      <c r="I10" s="34">
+      <c r="I10" s="33">
         <v>5</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="35" cm="1">
+      <c r="B11" s="34" cm="1">
         <f t="array" ref="B11">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>0.2</v>
       </c>
-      <c r="C11" s="35" cm="1">
+      <c r="C11" s="34" cm="1">
         <f t="array" ref="C11">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>0.25</v>
       </c>
-      <c r="D11" s="35" cm="1">
+      <c r="D11" s="34" cm="1">
         <f t="array" ref="D11">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="E11" s="35" cm="1">
+      <c r="E11" s="34" cm="1">
         <f t="array" ref="E11">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>1</v>
       </c>
-      <c r="F11" s="33">
+      <c r="F11" s="32">
         <v>0.33333333333333331</v>
       </c>
-      <c r="G11" s="33">
+      <c r="G11" s="32">
         <v>0.33333333333333331</v>
       </c>
-      <c r="H11" s="33">
-        <v>1</v>
-      </c>
-      <c r="I11" s="34">
-        <v>1</v>
-      </c>
-      <c r="K11" s="41" t="s">
+      <c r="H11" s="32">
+        <v>1</v>
+      </c>
+      <c r="I11" s="33">
+        <v>1</v>
+      </c>
+      <c r="K11" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="L11" s="41" t="s">
+      <c r="L11" s="39" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1897,40 +2030,40 @@
       <c r="A12" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="35" cm="1">
+      <c r="B12" s="34" cm="1">
         <f t="array" ref="B12">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>0.5</v>
       </c>
-      <c r="C12" s="35" cm="1">
+      <c r="C12" s="34" cm="1">
         <f t="array" ref="C12">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>0.5</v>
       </c>
-      <c r="D12" s="35" cm="1">
+      <c r="D12" s="34" cm="1">
         <f t="array" ref="D12">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>0.5</v>
       </c>
-      <c r="E12" s="35" cm="1">
+      <c r="E12" s="34" cm="1">
         <f t="array" ref="E12">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>3</v>
       </c>
-      <c r="F12" s="35" cm="1">
+      <c r="F12" s="34" cm="1">
         <f t="array" ref="F12">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>1</v>
       </c>
-      <c r="G12" s="33">
-        <v>1</v>
-      </c>
-      <c r="H12" s="33">
+      <c r="G12" s="32">
+        <v>1</v>
+      </c>
+      <c r="H12" s="32">
         <v>2</v>
       </c>
-      <c r="I12" s="34">
+      <c r="I12" s="33">
         <v>2</v>
       </c>
-      <c r="K12" s="42">
+      <c r="K12" s="40">
         <f>G30</f>
         <v>9.5929604988669676E-2</v>
       </c>
-      <c r="L12" s="39" t="str">
+      <c r="L12" s="38" t="str">
         <f>IF(G30&lt;=0.1,"Acceptable","Revise judgments")</f>
         <v>Acceptable</v>
       </c>
@@ -1939,34 +2072,34 @@
       <c r="A13" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="35" cm="1">
+      <c r="B13" s="34" cm="1">
         <f t="array" ref="B13">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>0.14285714285714285</v>
       </c>
-      <c r="C13" s="35" cm="1">
+      <c r="C13" s="34" cm="1">
         <f t="array" ref="C13">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>0.5</v>
       </c>
-      <c r="D13" s="35" cm="1">
+      <c r="D13" s="34" cm="1">
         <f t="array" ref="D13">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="E13" s="35" cm="1">
+      <c r="E13" s="34" cm="1">
         <f t="array" ref="E13">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>3</v>
       </c>
-      <c r="F13" s="35" cm="1">
+      <c r="F13" s="34" cm="1">
         <f t="array" ref="F13">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>1</v>
       </c>
-      <c r="G13" s="35" cm="1">
+      <c r="G13" s="34" cm="1">
         <f t="array" ref="G13">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>1</v>
       </c>
-      <c r="H13" s="33">
+      <c r="H13" s="32">
         <v>3</v>
       </c>
-      <c r="I13" s="34">
+      <c r="I13" s="33">
         <v>0.2</v>
       </c>
     </row>
@@ -1974,35 +2107,35 @@
       <c r="A14" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="35" cm="1">
+      <c r="B14" s="34" cm="1">
         <f t="array" ref="B14">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>0.14285714285714285</v>
       </c>
-      <c r="C14" s="35" cm="1">
+      <c r="C14" s="34" cm="1">
         <f t="array" ref="C14">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>0.14285714285714285</v>
       </c>
-      <c r="D14" s="35" cm="1">
+      <c r="D14" s="34" cm="1">
         <f t="array" ref="D14">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="E14" s="35" cm="1">
+      <c r="E14" s="34" cm="1">
         <f t="array" ref="E14">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>1</v>
       </c>
-      <c r="F14" s="35" cm="1">
+      <c r="F14" s="34" cm="1">
         <f t="array" ref="F14">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>0.5</v>
       </c>
-      <c r="G14" s="35" cm="1">
+      <c r="G14" s="34" cm="1">
         <f t="array" ref="G14">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="H14" s="35" cm="1">
+      <c r="H14" s="34" cm="1">
         <f t="array" ref="H14">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>1</v>
       </c>
-      <c r="I14" s="34">
+      <c r="I14" s="33">
         <v>1</v>
       </c>
     </row>
@@ -2010,35 +2143,35 @@
       <c r="A15" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="36" cm="1">
+      <c r="B15" s="35" cm="1">
         <f t="array" ref="B15">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>0.5</v>
       </c>
-      <c r="C15" s="36" cm="1">
+      <c r="C15" s="35" cm="1">
         <f t="array" ref="C15">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>0.25</v>
       </c>
-      <c r="D15" s="36" cm="1">
+      <c r="D15" s="35" cm="1">
         <f t="array" ref="D15">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>0.2</v>
       </c>
-      <c r="E15" s="36" cm="1">
+      <c r="E15" s="35" cm="1">
         <f t="array" ref="E15">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>1</v>
       </c>
-      <c r="F15" s="36" cm="1">
+      <c r="F15" s="35" cm="1">
         <f t="array" ref="F15">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>0.5</v>
       </c>
-      <c r="G15" s="36" cm="1">
+      <c r="G15" s="35" cm="1">
         <f t="array" ref="G15">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>5</v>
       </c>
-      <c r="H15" s="36" cm="1">
+      <c r="H15" s="35" cm="1">
         <f t="array" ref="H15">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>1</v>
       </c>
-      <c r="I15" s="37" cm="1">
+      <c r="I15" s="36" cm="1">
         <f t="array" ref="I15">IF(ROW()-ROW($B$8)=COLUMN()-COLUMN($B$8),1,IF(ROW()-ROW($B$8)&gt;COLUMN()-COLUMN($B$8),IFERROR(1/INDEX($B$8:$I$15,COLUMN()-COLUMN($B$8)+1,ROW()-ROW($B$8)+1),""),""))</f>
         <v>1</v>
       </c>
